--- a/StructureDefinition-lmdi-medication.xlsx
+++ b/StructureDefinition-lmdi-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.7</t>
+    <t>1.0.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -1189,43 +1189,43 @@
     <t>Medication.form.coding.userSelected</t>
   </si>
   <si>
-    <t>Medication.form.coding:7448</t>
-  </si>
-  <si>
-    <t>7448</t>
+    <t>Medication.form.coding:OID7448</t>
+  </si>
+  <si>
+    <t>OID7448</t>
   </si>
   <si>
     <t>Kodeverk Legemiddelform (OID:7448) fra FEST</t>
   </si>
   <si>
-    <t>Medication.form.coding:7448.id</t>
-  </si>
-  <si>
-    <t>Medication.form.coding:7448.extension</t>
-  </si>
-  <si>
-    <t>Medication.form.coding:7448.system</t>
+    <t>Medication.form.coding:OID7448.id</t>
+  </si>
+  <si>
+    <t>Medication.form.coding:OID7448.extension</t>
+  </si>
+  <si>
+    <t>Medication.form.coding:OID7448.system</t>
   </si>
   <si>
     <t>urn:oid:2.16.578.1.12.4.1.1.7448</t>
   </si>
   <si>
-    <t>Medication.form.coding:7448.version</t>
-  </si>
-  <si>
-    <t>Medication.form.coding:7448.code</t>
+    <t>Medication.form.coding:OID7448.version</t>
+  </si>
+  <si>
+    <t>Medication.form.coding:OID7448.code</t>
   </si>
   <si>
     <t>Verdi fra kodeverket</t>
   </si>
   <si>
-    <t>Medication.form.coding:7448.display</t>
+    <t>Medication.form.coding:OID7448.display</t>
   </si>
   <si>
     <t>Beskrivelse av koden (navn) fra kodeverket</t>
   </si>
   <si>
-    <t>Medication.form.coding:7448.userSelected</t>
+    <t>Medication.form.coding:OID7448.userSelected</t>
   </si>
   <si>
     <t>Medication.form.coding:SCT</t>

--- a/StructureDefinition-lmdi-medication.xlsx
+++ b/StructureDefinition-lmdi-medication.xlsx
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lmdi-medication-code-or-ingredient:Medication skal ha code.coding eller ingredient {code.coding.exists() or ingredient.exists()}</t>
   </si>
   <si>
     <t>NewRx/MedicationPrescribed@@ -465,7 +465,7 @@
 </t>
   </si>
   <si>
-    <t>Klassifisering av legemidlet, fortrinnsvis ved bruk av ATC-kode fra WHO ATC kodesystem. Ett legemiddel kan ha inntil én ATC-kode.</t>
+    <t>Klassifisering av legemidlet ved bruk av ATC-kode fra WHO ATC kodesystem. Ett legemiddel kan ha inntil én ATC-kode.</t>
   </si>
   <si>
     <t>Denne extension brukes for å angi legemidlets klassifisering i henhold til standardiserte kodesystemer, primært ATC-koder fra WHO.</t>
@@ -2848,7 +2848,7 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-lmdi-medication.xlsx
+++ b/StructureDefinition-lmdi-medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4637" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4637" uniqueCount="461">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -465,7 +465,10 @@
 </t>
   </si>
   <si>
-    <t>Klassifisering av legemidlet ved bruk av ATC-kode fra WHO ATC kodesystem. Ett legemiddel kan ha inntil én ATC-kode.</t>
+    <t>Klassifisering av legemidlet ved bruk av ATC-kode fra WHO ATC kodesystem.</t>
+  </si>
+  <si>
+    <t>Klassifisering av legemidlet ved bruk av ATC-kode fra WHO ATC kodesystem. Et legemiddel har i utgangspunktet kun én ATC-kode.</t>
   </si>
   <si>
     <t>Denne extension brukes for å angi legemidlets klassifisering i henhold til standardiserte kodesystemer, primært ATC-koder fra WHO.</t>
@@ -735,7 +738,7 @@
     <t>Medication.code.coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
+    <t>NavnFormStyrke fra FEST</t>
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
@@ -856,6 +859,9 @@
     <t>Medication.code.coding:FestLegemiddelMerkevare.display</t>
   </si>
   <si>
+    <t>Varenavn eller NavnFormStyrke fra FEST</t>
+  </si>
+  <si>
     <t>Medication.code.coding:FestLegemiddelMerkevare.userSelected</t>
   </si>
   <si>
@@ -931,10 +937,10 @@
     <t>Medication.code.coding:Varenummer.userSelected</t>
   </si>
   <si>
-    <t>Medication.code.coding:FestVirkestoff</t>
-  </si>
-  <si>
-    <t>FestVirkestoff</t>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff</t>
+  </si>
+  <si>
+    <t>FestLegemiddelVirkestoff</t>
   </si>
   <si>
     <t>FEST-id for legemiddel virkestoff</t>
@@ -943,28 +949,28 @@
     <t>Unik identifikator (LegemiddelVirkestoff_ID) for rekvirering på virkestoffnivå i FEST.</t>
   </si>
   <si>
-    <t>Medication.code.coding:FestVirkestoff.id</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:FestVirkestoff.extension</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:FestVirkestoff.system</t>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.id</t>
+  </si>
+  <si>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.extension</t>
+  </si>
+  <si>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.system</t>
   </si>
   <si>
     <t>http://dmp.no/fhir/NamingSystem/festLegemiddelVirkestoff</t>
   </si>
   <si>
-    <t>Medication.code.coding:FestVirkestoff.version</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:FestVirkestoff.code</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:FestVirkestoff.display</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:FestVirkestoff.userSelected</t>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.version</t>
+  </si>
+  <si>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.code</t>
+  </si>
+  <si>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.display</t>
+  </si>
+  <si>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.userSelected</t>
   </si>
   <si>
     <t>Medication.code.coding:LokaltLegemiddel</t>
@@ -988,7 +994,7 @@
     <t>Medication.code.coding:LokaltLegemiddel.system</t>
   </si>
   <si>
-    <t>http://fh.no/fhir/NamingSystem/lokaltVirkemiddel</t>
+    <t>http://fhi.no/fhir/NamingSystem/lokaltLegemiddel</t>
   </si>
   <si>
     <t>Medication.code.coding:LokaltLegemiddel.version</t>
@@ -1043,6 +1049,9 @@
   </si>
   <si>
     <t>Medication.code.coding:SCT.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
   </si>
   <si>
     <t>Medication.code.coding:SCT.userSelected</t>
@@ -1284,7 +1293,7 @@
     <t>Virkestoff(er) som inngår i legemiddelet. Skal fylles ut hvis code ikke har verdi. Bør fylles ut hvis code.coding[LokaltLegemiddel] har verdi.</t>
   </si>
   <si>
-    <t>For legemidler identifisert med FEST-koder (FestLegemiddeldose, FestLegemiddelMerkevare, FestLegemiddelpakning, FestVirkestoff, Varenummer) eller SNOMED CT er ingredient valgfritt, da virkestoffinformasjon kan hentes fra disse katalogene. For lokale legemidler anbefales det å oppgi ingredient for bedre sporbarhet.</t>
+    <t>For legemidler identifisert med FEST-koder (FestLegemiddeldose, FestLegemiddelMerkevare, FestLegemiddelpakning, FestLegemiddelVirkestoff, Varenummer) eller SNOMED CT er ingredient valgfritt, da virkestoffinformasjon kan hentes fra disse katalogene. For lokale legemidler anbefales det å oppgi ingredient for bedre sporbarhet.</t>
   </si>
   <si>
     <t>.scopesRole[typeCode=INGR]</t>
@@ -2848,7 +2857,7 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>77</v>
@@ -2866,10 +2875,10 @@
         <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2928,7 +2937,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>138</v>
@@ -2948,14 +2957,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2977,16 +2986,16 @@
         <v>132</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -3035,7 +3044,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3064,10 +3073,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3090,16 +3099,16 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3149,7 +3158,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3167,10 +3176,10 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -3178,10 +3187,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3204,16 +3213,16 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3239,11 +3248,11 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3261,7 +3270,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3276,24 +3285,24 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3316,13 +3325,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3373,7 +3382,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3391,7 +3400,7 @@
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3402,14 +3411,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3431,13 +3440,13 @@
         <v>132</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3478,16 +3487,16 @@
         <v>135</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3505,7 +3514,7 @@
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3516,10 +3525,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3542,19 +3551,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3591,17 +3600,17 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3619,24 +3628,24 @@
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>77</v>
@@ -3658,19 +3667,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3719,7 +3728,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3737,21 +3746,21 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3774,13 +3783,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3831,7 +3840,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3849,7 +3858,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3860,14 +3869,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3889,13 +3898,13 @@
         <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3936,16 +3945,16 @@
         <v>135</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3963,7 +3972,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3974,10 +3983,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4003,16 +4012,16 @@
         <v>101</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -4022,7 +4031,7 @@
         <v>77</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>77</v>
@@ -4061,7 +4070,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4079,21 +4088,21 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4116,16 +4125,16 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4175,7 +4184,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4193,21 +4202,21 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4233,14 +4242,14 @@
         <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4289,7 +4298,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4307,21 +4316,21 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4344,17 +4353,17 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4403,7 +4412,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4421,21 +4430,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4458,19 +4467,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4519,7 +4528,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4537,24 +4546,24 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>77</v>
@@ -4576,19 +4585,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4637,7 +4646,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4655,21 +4664,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4692,13 +4701,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4749,7 +4758,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4767,7 +4776,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4778,14 +4787,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4807,13 +4816,13 @@
         <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4854,16 +4863,16 @@
         <v>135</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4881,7 +4890,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4892,10 +4901,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4921,16 +4930,16 @@
         <v>101</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4940,7 +4949,7 @@
         <v>77</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>77</v>
@@ -4979,7 +4988,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4997,21 +5006,21 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5034,16 +5043,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5093,7 +5102,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5111,21 +5120,21 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5151,14 +5160,14 @@
         <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5207,7 +5216,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5225,21 +5234,21 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5262,17 +5271,17 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5321,7 +5330,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5339,21 +5348,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5376,19 +5385,19 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5437,7 +5446,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5455,24 +5464,24 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>77</v>
@@ -5494,19 +5503,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5555,7 +5564,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5573,21 +5582,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5610,13 +5619,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5667,7 +5676,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5685,7 +5694,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5696,14 +5705,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5725,13 +5734,13 @@
         <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5772,16 +5781,16 @@
         <v>135</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5799,7 +5808,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5810,10 +5819,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5839,16 +5848,16 @@
         <v>101</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5858,7 +5867,7 @@
         <v>77</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>77</v>
@@ -5897,7 +5906,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5915,21 +5924,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5952,16 +5961,16 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6011,7 +6020,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6029,21 +6038,21 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6069,14 +6078,14 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6125,7 +6134,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6143,21 +6152,21 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6180,17 +6189,17 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6239,7 +6248,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6257,21 +6266,21 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6294,19 +6303,19 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6355,7 +6364,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6373,24 +6382,24 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>77</v>
@@ -6412,19 +6421,19 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6473,7 +6482,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6491,21 +6500,21 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6528,13 +6537,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6585,7 +6594,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6603,7 +6612,7 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6614,14 +6623,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6643,13 +6652,13 @@
         <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6690,16 +6699,16 @@
         <v>135</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6717,7 +6726,7 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6728,10 +6737,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6757,16 +6766,16 @@
         <v>101</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6776,7 +6785,7 @@
         <v>77</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>77</v>
@@ -6815,7 +6824,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6833,21 +6842,21 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6870,16 +6879,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6929,7 +6938,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6947,21 +6956,21 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6987,14 +6996,14 @@
         <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7043,7 +7052,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7061,21 +7070,21 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7098,17 +7107,17 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7157,7 +7166,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7175,21 +7184,21 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7212,19 +7221,19 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7273,7 +7282,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7291,24 +7300,24 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -7330,19 +7339,19 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7391,7 +7400,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7409,21 +7418,21 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7446,13 +7455,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7503,7 +7512,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7521,7 +7530,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7532,14 +7541,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7561,13 +7570,13 @@
         <v>132</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7608,16 +7617,16 @@
         <v>135</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7635,7 +7644,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7646,10 +7655,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7675,16 +7684,16 @@
         <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7694,7 +7703,7 @@
         <v>77</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>77</v>
@@ -7733,7 +7742,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7751,21 +7760,21 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7788,16 +7797,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7847,7 +7856,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7865,21 +7874,21 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7905,14 +7914,14 @@
         <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7961,7 +7970,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7979,21 +7988,21 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8016,17 +8025,17 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8075,7 +8084,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8093,21 +8102,21 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8130,19 +8139,19 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8191,7 +8200,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8209,24 +8218,24 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
@@ -8248,19 +8257,19 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8309,7 +8318,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8327,21 +8336,21 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8364,13 +8373,13 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8421,7 +8430,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8439,7 +8448,7 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8450,14 +8459,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8479,13 +8488,13 @@
         <v>132</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8526,16 +8535,16 @@
         <v>135</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8553,7 +8562,7 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8564,10 +8573,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8593,16 +8602,16 @@
         <v>101</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8612,7 +8621,7 @@
         <v>77</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>77</v>
@@ -8651,7 +8660,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8669,21 +8678,21 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8706,16 +8715,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8765,7 +8774,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8783,21 +8792,21 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8823,14 +8832,14 @@
         <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8879,7 +8888,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8897,21 +8906,21 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8934,17 +8943,17 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8993,7 +9002,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9011,21 +9020,21 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9048,19 +9057,19 @@
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9109,7 +9118,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9127,24 +9136,24 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>77</v>
@@ -9166,19 +9175,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9227,7 +9236,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9245,21 +9254,21 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9282,13 +9291,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9339,7 +9348,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9357,7 +9366,7 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9368,14 +9377,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9397,13 +9406,13 @@
         <v>132</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9444,16 +9453,16 @@
         <v>135</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9471,7 +9480,7 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9482,10 +9491,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9511,16 +9520,16 @@
         <v>101</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9530,7 +9539,7 @@
         <v>77</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>77</v>
@@ -9569,7 +9578,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9587,21 +9596,21 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9624,16 +9633,16 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9683,7 +9692,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9701,21 +9710,21 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9741,14 +9750,14 @@
         <v>107</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9797,7 +9806,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9815,21 +9824,21 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9852,17 +9861,17 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9911,7 +9920,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9929,21 +9938,21 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9966,19 +9975,19 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10027,7 +10036,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10045,24 +10054,24 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>77</v>
@@ -10084,19 +10093,19 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10145,7 +10154,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10163,21 +10172,21 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10200,13 +10209,13 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10257,7 +10266,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10275,7 +10284,7 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10286,14 +10295,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10315,13 +10324,13 @@
         <v>132</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10362,16 +10371,16 @@
         <v>135</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10389,7 +10398,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10400,10 +10409,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10429,16 +10438,16 @@
         <v>101</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10448,7 +10457,7 @@
         <v>77</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>77</v>
@@ -10487,7 +10496,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10505,21 +10514,21 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10542,16 +10551,16 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10601,7 +10610,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10619,21 +10628,21 @@
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10659,14 +10668,14 @@
         <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -10715,7 +10724,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10733,21 +10742,21 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10770,17 +10779,17 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>228</v>
+        <v>333</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -10829,7 +10838,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10847,21 +10856,21 @@
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10884,19 +10893,19 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -10945,7 +10954,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10963,21 +10972,21 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11000,19 +11009,19 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11061,7 +11070,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11079,21 +11088,21 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11119,13 +11128,13 @@
         <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11151,13 +11160,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -11175,7 +11184,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11193,7 +11202,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -11204,10 +11213,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11230,13 +11239,13 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11287,7 +11296,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11302,24 +11311,24 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11342,16 +11351,16 @@
         <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11377,13 +11386,13 @@
         <v>77</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>77</v>
@@ -11401,7 +11410,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11416,24 +11425,24 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11456,13 +11465,13 @@
         <v>77</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11513,7 +11522,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11531,7 +11540,7 @@
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
@@ -11542,14 +11551,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -11571,13 +11580,13 @@
         <v>132</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11618,16 +11627,16 @@
         <v>135</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11645,7 +11654,7 @@
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
@@ -11656,10 +11665,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11682,19 +11691,19 @@
         <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>77</v>
@@ -11731,7 +11740,7 @@
         <v>77</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
@@ -11741,7 +11750,7 @@
         <v>136</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11759,21 +11768,21 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11796,13 +11805,13 @@
         <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11853,7 +11862,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11871,7 +11880,7 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -11882,14 +11891,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11911,13 +11920,13 @@
         <v>132</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11958,16 +11967,16 @@
         <v>135</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -11985,7 +11994,7 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -11996,10 +12005,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12025,16 +12034,16 @@
         <v>101</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>77</v>
@@ -12083,7 +12092,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12101,21 +12110,21 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12138,16 +12147,16 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12197,7 +12206,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12215,21 +12224,21 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12255,14 +12264,14 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -12311,7 +12320,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12329,21 +12338,21 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12366,17 +12375,17 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>228</v>
+        <v>333</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -12425,7 +12434,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12443,21 +12452,21 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12480,19 +12489,19 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
@@ -12541,7 +12550,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12559,24 +12568,24 @@
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>77</v>
@@ -12598,19 +12607,19 @@
         <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>77</v>
@@ -12659,7 +12668,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12677,21 +12686,21 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12714,13 +12723,13 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12771,7 +12780,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12789,7 +12798,7 @@
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -12800,14 +12809,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12829,13 +12838,13 @@
         <v>132</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -12876,16 +12885,16 @@
         <v>135</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12903,7 +12912,7 @@
         <v>77</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
@@ -12914,10 +12923,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12943,16 +12952,16 @@
         <v>101</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -12962,7 +12971,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -13001,7 +13010,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13019,21 +13028,21 @@
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13056,16 +13065,16 @@
         <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13115,7 +13124,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13133,21 +13142,21 @@
         <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13173,14 +13182,14 @@
         <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -13229,7 +13238,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13247,21 +13256,21 @@
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13284,17 +13293,17 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -13343,7 +13352,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13361,21 +13370,21 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13398,19 +13407,19 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -13459,7 +13468,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13477,24 +13486,24 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>77</v>
@@ -13516,19 +13525,19 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13577,7 +13586,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13595,21 +13604,21 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13632,13 +13641,13 @@
         <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13689,7 +13698,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13707,7 +13716,7 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -13718,14 +13727,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -13747,13 +13756,13 @@
         <v>132</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -13794,16 +13803,16 @@
         <v>135</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -13821,7 +13830,7 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -13832,10 +13841,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13861,16 +13870,16 @@
         <v>101</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>77</v>
@@ -13880,7 +13889,7 @@
         <v>77</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>77</v>
@@ -13919,7 +13928,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -13937,21 +13946,21 @@
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13974,16 +13983,16 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14033,7 +14042,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14051,21 +14060,21 @@
         <v>77</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14091,14 +14100,14 @@
         <v>107</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -14147,7 +14156,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14165,21 +14174,21 @@
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14202,17 +14211,17 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>228</v>
+        <v>333</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -14261,7 +14270,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14279,21 +14288,21 @@
         <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14316,19 +14325,19 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>77</v>
@@ -14377,7 +14386,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14395,21 +14404,21 @@
         <v>77</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14432,19 +14441,19 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -14493,7 +14502,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14511,21 +14520,21 @@
         <v>77</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14548,13 +14557,13 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14605,7 +14614,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14623,7 +14632,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -14634,10 +14643,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14660,16 +14669,16 @@
         <v>77</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -14719,7 +14728,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14737,7 +14746,7 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -14748,10 +14757,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14774,13 +14783,13 @@
         <v>77</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -14831,7 +14840,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -14849,7 +14858,7 @@
         <v>77</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>77</v>
@@ -14860,14 +14869,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -14889,13 +14898,13 @@
         <v>132</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14945,7 +14954,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -14963,7 +14972,7 @@
         <v>77</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
@@ -14974,14 +14983,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15003,16 +15012,16 @@
         <v>132</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>77</v>
@@ -15061,7 +15070,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15090,10 +15099,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15116,17 +15125,17 @@
         <v>77</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>77</v>
@@ -15163,7 +15172,7 @@
         <v>77</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AC117" s="2"/>
       <c r="AD117" t="s" s="2">
@@ -15173,7 +15182,7 @@
         <v>136</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>87</v>
@@ -15188,27 +15197,27 @@
         <v>99</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>77</v>
@@ -15230,17 +15239,17 @@
         <v>77</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>77</v>
@@ -15289,7 +15298,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>87</v>
@@ -15304,27 +15313,27 @@
         <v>99</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>77</v>
@@ -15346,17 +15355,17 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -15385,7 +15394,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>77</v>
@@ -15403,7 +15412,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>87</v>
@@ -15418,24 +15427,24 @@
         <v>99</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15458,17 +15467,17 @@
         <v>77</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>77</v>
@@ -15517,7 +15526,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15535,7 +15544,7 @@
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>77</v>
@@ -15546,10 +15555,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15572,13 +15581,13 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15629,7 +15638,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -15644,24 +15653,24 @@
         <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15684,13 +15693,13 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -15741,7 +15750,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -15756,10 +15765,10 @@
         <v>99</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -15770,10 +15779,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15796,13 +15805,13 @@
         <v>77</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -15853,7 +15862,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -15871,7 +15880,7 @@
         <v>77</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>77</v>
@@ -15882,14 +15891,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -15911,13 +15920,13 @@
         <v>132</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -15967,7 +15976,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -15985,7 +15994,7 @@
         <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>77</v>
@@ -15996,14 +16005,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -16025,16 +16034,16 @@
         <v>132</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -16083,7 +16092,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16112,10 +16121,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16138,13 +16147,13 @@
         <v>77</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16195,7 +16204,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16210,24 +16219,24 @@
         <v>99</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16250,13 +16259,13 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16307,7 +16316,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -16322,16 +16331,16 @@
         <v>99</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-lmdi-medication.xlsx
+++ b/StructureDefinition-lmdi-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-medication.xlsx
+++ b/StructureDefinition-lmdi-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.1.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-medication.xlsx
+++ b/StructureDefinition-lmdi-medication.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$132</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4637" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4814" uniqueCount="478">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -1383,16 +1383,69 @@
     <t>Medication.ingredient.strength</t>
   </si>
   <si>
-    <t>Quantity of ingredient present</t>
-  </si>
-  <si>
-    <t>Specifies how many (or how much) of the items there are in this Medication.  For example, 250 mg per tablet.  This is expressed as a ratio where the numerator is 250mg and the denominator is 1 tablet.</t>
+    <t>Styrken av ingrediensen i det rekvirerte/administrerte legemidlet.</t>
   </si>
   <si>
     <t>//element(*,DrugCodedType)/Strength</t>
   </si>
   <si>
     <t>RXC-3-Component Amount &amp; RXC-4-Component Units  if medication: RXO-2-Requested Give Amount - Minimum &amp; RXO-4-Requested Give Units / RXO-3-Requested Give Amount - Maximum &amp; RXO-4-Requested Give Units / RXO-11-Requested Dispense Amount &amp; RXO-12-Requested Dispense Units / RXE-3-Give Amount - Minimum &amp; RXE-5-Give Units / RXE-4-Give Amount - Maximum &amp; RXE-5-Give Units / RXE-10-Dispense Amount &amp; RXE-10-Dispense Units</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength.extension:mengde</t>
+  </si>
+  <si>
+    <t>mengde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-ingredient-strength}
+</t>
+  </si>
+  <si>
+    <t>Mengde ingrediens i det rekvirerte/administrerte legemidlet.</t>
+  </si>
+  <si>
+    <t>Mengde ingrediens i det rekvirerte/administrerte legemidlet, angitt som volum eller mengde virkestoff (Quantity), eller som kode (qs, trace). Brukes i stedet for teller og nevner i strength.</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength.numerator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Numerator value</t>
+  </si>
+  <si>
+    <t>The value of the numerator.</t>
+  </si>
+  <si>
+    <t>Ratio.numerator</t>
+  </si>
+  <si>
+    <t>.numerator</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength.denominator</t>
+  </si>
+  <si>
+    <t>Denominator value</t>
+  </si>
+  <si>
+    <t>The value of the denominator.</t>
+  </si>
+  <si>
+    <t>Ratio.denominator</t>
+  </si>
+  <si>
+    <t>.denominator</t>
   </si>
   <si>
     <t>Medication.batch</t>
@@ -1769,11 +1822,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN127"/>
+  <dimension ref="A1:AN132"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.77734375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.73046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -15587,7 +15640,7 @@
         <v>440</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15653,7 +15706,7 @@
         <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>408</v>
@@ -15662,15 +15715,15 @@
         <v>77</v>
       </c>
       <c r="AN121" t="s" s="2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
         <v>443</v>
       </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s" s="2">
-        <v>444</v>
-      </c>
       <c r="B122" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15684,7 +15737,7 @@
         <v>87</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>77</v>
@@ -15693,13 +15746,13 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>410</v>
+        <v>172</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>445</v>
+        <v>173</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>446</v>
+        <v>174</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -15750,7 +15803,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>444</v>
+        <v>175</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -15762,13 +15815,13 @@
         <v>77</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>355</v>
+        <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>447</v>
+        <v>176</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -15779,21 +15832,21 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>77</v>
@@ -15805,15 +15858,17 @@
         <v>77</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -15850,31 +15905,31 @@
         <v>77</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>77</v>
@@ -15891,21 +15946,23 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C124" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="D124" t="s" s="2">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>77</v>
@@ -15917,17 +15974,15 @@
         <v>77</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>132</v>
+        <v>447</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>178</v>
+        <v>448</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>77</v>
@@ -15994,7 +16049,7 @@
         <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>77</v>
@@ -16012,39 +16067,35 @@
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>417</v>
+        <v>77</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J125" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>132</v>
+        <v>451</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>77</v>
       </c>
@@ -16092,25 +16143,25 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>130</v>
+        <v>455</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>77</v>
@@ -16121,10 +16172,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16144,16 +16195,16 @@
         <v>77</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>172</v>
+        <v>451</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16204,7 +16255,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16219,24 +16270,24 @@
         <v>99</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>355</v>
+        <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>158</v>
+        <v>460</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>454</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16250,7 +16301,7 @@
         <v>87</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>77</v>
@@ -16259,13 +16310,13 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16316,7 +16367,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -16334,17 +16385,583 @@
         <v>355</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>460</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>477</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN127">
+  <autoFilter ref="A1:AN132">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16354,7 +16971,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI126">
+  <conditionalFormatting sqref="A2:AI131">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
